--- a/config/xlsx/items.xlsx
+++ b/config/xlsx/items.xlsx
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>5</v>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>15</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>35</v>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>80</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>180</v>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>400</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>279</v>
+        <v>404</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>900</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>670</v>
+        <v>970</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>2000</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>1608</v>
+        <v>2328</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>4500</v>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>3860</v>
+        <v>5588</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>10000</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>9264</v>
+        <v>13412</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>22000</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>22234</v>
+        <v>32189</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>50000</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>53362</v>
+        <v>77254</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>110000</v>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>128069</v>
+        <v>185410</v>
       </c>
       <c r="I47" s="3" t="n">
         <v>250000</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>307366</v>
+        <v>444984</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>550000</v>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>737679</v>
+        <v>1067962</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>1200000</v>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>青灵枝是灵木一脉的1级材料，可用于对应层次的修真制作。</t>
+          <t>青灵枝是灵木一脉的1级材料。</t>
         </is>
       </c>
       <c r="H194" s="3" t="n">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>云纹木是灵木一脉的2级材料，可用于对应层次的修真制作。</t>
+          <t>云纹木是灵木一脉的2级材料。</t>
         </is>
       </c>
       <c r="H195" s="3" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>赤霞杉是灵木一脉的3级材料，可用于对应层次的修真制作。</t>
+          <t>赤霞杉是灵木一脉的3级材料。</t>
         </is>
       </c>
       <c r="H196" s="3" t="n">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>月桂灵木是灵木一脉的4级材料，可用于对应层次的修真制作。</t>
+          <t>月桂灵木是灵木一脉的4级材料。</t>
         </is>
       </c>
       <c r="H197" s="3" t="n">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>雷击桃木是灵木一脉的5级材料，可用于对应层次的修真制作。</t>
+          <t>雷击桃木是灵木一脉的5级材料。</t>
         </is>
       </c>
       <c r="H198" s="3" t="n">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>玄冰梧桐是灵木一脉的6级材料，可用于对应层次的修真制作。</t>
+          <t>玄冰梧桐是灵木一脉的6级材料。</t>
         </is>
       </c>
       <c r="H199" s="3" t="n">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>地脉沉香是灵木一脉的7级材料，可用于对应层次的修真制作。</t>
+          <t>地脉沉香是灵木一脉的7级材料。</t>
         </is>
       </c>
       <c r="H200" s="3" t="n">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>星辉紫檀是灵木一脉的8级材料，可用于对应层次的修真制作。</t>
+          <t>星辉紫檀是灵木一脉的8级材料。</t>
         </is>
       </c>
       <c r="H201" s="3" t="n">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>龙血古木是灵木一脉的9级材料，可用于对应层次的修真制作。</t>
+          <t>龙血古木是灵木一脉的9级材料。</t>
         </is>
       </c>
       <c r="H202" s="3" t="n">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>凤栖神木是灵木一脉的10级材料，可用于对应层次的修真制作。</t>
+          <t>凤栖神木是灵木一脉的10级材料。</t>
         </is>
       </c>
       <c r="H203" s="3" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>九幽冥木是灵木一脉的11级材料，可用于对应层次的修真制作。</t>
+          <t>九幽冥木是灵木一脉的11级材料。</t>
         </is>
       </c>
       <c r="H204" s="3" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>扶桑阳木是灵木一脉的12级材料，可用于对应层次的修真制作。</t>
+          <t>扶桑阳木是灵木一脉的12级材料。</t>
         </is>
       </c>
       <c r="H205" s="3" t="n">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>建木灵芯是灵木一脉的13级材料，可用于对应层次的修真制作。</t>
+          <t>建木灵芯是灵木一脉的13级材料。</t>
         </is>
       </c>
       <c r="H206" s="3" t="n">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>菩提道木是灵木一脉的14级材料，可用于对应层次的修真制作。</t>
+          <t>菩提道木是灵木一脉的14级材料。</t>
         </is>
       </c>
       <c r="H207" s="3" t="n">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙祖木是灵木一脉的15级材料，可用于对应层次的修真制作。</t>
+          <t>鸿蒙祖木是灵木一脉的15级材料。</t>
         </is>
       </c>
       <c r="H208" s="3" t="n">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>世界树心是灵木一脉的16级材料，可用于对应层次的修真制作。</t>
+          <t>世界树心是灵木一脉的16级材料。</t>
         </is>
       </c>
       <c r="H209" s="3" t="n">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>松露灵脂是灵脂一脉的1级材料，可用于对应层次的修真制作。</t>
+          <t>松露灵脂是灵脂一脉的1级材料。</t>
         </is>
       </c>
       <c r="H210" s="3" t="n">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>青檀脂是灵脂一脉的2级材料，可用于对应层次的修真制作。</t>
+          <t>青檀脂是灵脂一脉的2级材料。</t>
         </is>
       </c>
       <c r="H211" s="3" t="n">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>赤枫脂是灵脂一脉的3级材料，可用于对应层次的修真制作。</t>
+          <t>赤枫脂是灵脂一脉的3级材料。</t>
         </is>
       </c>
       <c r="H212" s="3" t="n">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>月桂凝脂是灵脂一脉的4级材料，可用于对应层次的修真制作。</t>
+          <t>月桂凝脂是灵脂一脉的4级材料。</t>
         </is>
       </c>
       <c r="H213" s="3" t="n">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>桃木雷脂是灵脂一脉的5级材料，可用于对应层次的修真制作。</t>
+          <t>桃木雷脂是灵脂一脉的5级材料。</t>
         </is>
       </c>
       <c r="H214" s="3" t="n">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>冰梧寒脂是灵脂一脉的6级材料，可用于对应层次的修真制作。</t>
+          <t>冰梧寒脂是灵脂一脉的6级材料。</t>
         </is>
       </c>
       <c r="H215" s="3" t="n">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>沉香地髓是灵脂一脉的7级材料，可用于对应层次的修真制作。</t>
+          <t>沉香地髓是灵脂一脉的7级材料。</t>
         </is>
       </c>
       <c r="H216" s="3" t="n">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>紫檀星脂是灵脂一脉的8级材料，可用于对应层次的修真制作。</t>
+          <t>紫檀星脂是灵脂一脉的8级材料。</t>
         </is>
       </c>
       <c r="H217" s="3" t="n">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>龙血木脂是灵脂一脉的9级材料，可用于对应层次的修真制作。</t>
+          <t>龙血木脂是灵脂一脉的9级材料。</t>
         </is>
       </c>
       <c r="H218" s="3" t="n">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>凤栖香脂是灵脂一脉的10级材料，可用于对应层次的修真制作。</t>
+          <t>凤栖香脂是灵脂一脉的10级材料。</t>
         </is>
       </c>
       <c r="H219" s="3" t="n">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>九幽玄脂是灵脂一脉的11级材料，可用于对应层次的修真制作。</t>
+          <t>九幽玄脂是灵脂一脉的11级材料。</t>
         </is>
       </c>
       <c r="H220" s="3" t="n">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>扶桑日脂是灵脂一脉的12级材料，可用于对应层次的修真制作。</t>
+          <t>扶桑日脂是灵脂一脉的12级材料。</t>
         </is>
       </c>
       <c r="H221" s="3" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>建木玉脂是灵脂一脉的13级材料，可用于对应层次的修真制作。</t>
+          <t>建木玉脂是灵脂一脉的13级材料。</t>
         </is>
       </c>
       <c r="H222" s="3" t="n">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>菩提心脂是灵脂一脉的14级材料，可用于对应层次的修真制作。</t>
+          <t>菩提心脂是灵脂一脉的14级材料。</t>
         </is>
       </c>
       <c r="H223" s="3" t="n">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙源脂是灵脂一脉的15级材料，可用于对应层次的修真制作。</t>
+          <t>鸿蒙源脂是灵脂一脉的15级材料。</t>
         </is>
       </c>
       <c r="H224" s="3" t="n">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>太初神脂是灵脂一脉的16级材料，可用于对应层次的修真制作。</t>
+          <t>太初神脂是灵脂一脉的16级材料。</t>
         </is>
       </c>
       <c r="H225" s="3" t="n">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>青鳞灵鱼是灵鱼一脉的1级材料，可用于对应层次的修真制作。</t>
+          <t>青鳞灵鱼是灵鱼一脉的1级材料。</t>
         </is>
       </c>
       <c r="H226" s="3" t="n">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>银须鲫是灵鱼一脉的2级材料，可用于对应层次的修真制作。</t>
+          <t>银须鲫是灵鱼一脉的2级材料。</t>
         </is>
       </c>
       <c r="H227" s="3" t="n">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>赤尾鲤是灵鱼一脉的3级材料，可用于对应层次的修真制作。</t>
+          <t>赤尾鲤是灵鱼一脉的3级材料。</t>
         </is>
       </c>
       <c r="H228" s="3" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>月纹鳜是灵鱼一脉的4级材料，可用于对应层次的修真制作。</t>
+          <t>月纹鳜是灵鱼一脉的4级材料。</t>
         </is>
       </c>
       <c r="H229" s="3" t="n">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>雷鳍鲶是灵鱼一脉的5级材料，可用于对应层次的修真制作。</t>
+          <t>雷鳍鲶是灵鱼一脉的5级材料。</t>
         </is>
       </c>
       <c r="H230" s="3" t="n">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>冰魄鲑是灵鱼一脉的6级材料，可用于对应层次的修真制作。</t>
+          <t>冰魄鲑是灵鱼一脉的6级材料。</t>
         </is>
       </c>
       <c r="H231" s="3" t="n">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>地脉鳅是灵鱼一脉的7级材料，可用于对应层次的修真制作。</t>
+          <t>地脉鳅是灵鱼一脉的7级材料。</t>
         </is>
       </c>
       <c r="H232" s="3" t="n">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>星斑鲷是灵鱼一脉的8级材料，可用于对应层次的修真制作。</t>
+          <t>星斑鲷是灵鱼一脉的8级材料。</t>
         </is>
       </c>
       <c r="H233" s="3" t="n">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>龙须鲤是灵鱼一脉的9级材料，可用于对应层次的修真制作。</t>
+          <t>龙须鲤是灵鱼一脉的9级材料。</t>
         </is>
       </c>
       <c r="H234" s="3" t="n">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>凤尾锦鲤是灵鱼一脉的10级材料，可用于对应层次的修真制作。</t>
+          <t>凤尾锦鲤是灵鱼一脉的10级材料。</t>
         </is>
       </c>
       <c r="H235" s="3" t="n">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>九幽玄鱼是灵鱼一脉的11级材料，可用于对应层次的修真制作。</t>
+          <t>九幽玄鱼是灵鱼一脉的11级材料。</t>
         </is>
       </c>
       <c r="H236" s="3" t="n">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>扶桑金鲤是灵鱼一脉的12级材料，可用于对应层次的修真制作。</t>
+          <t>扶桑金鲤是灵鱼一脉的12级材料。</t>
         </is>
       </c>
       <c r="H237" s="3" t="n">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>建木游龙是灵鱼一脉的13级材料，可用于对应层次的修真制作。</t>
+          <t>建木游龙是灵鱼一脉的13级材料。</t>
         </is>
       </c>
       <c r="H238" s="3" t="n">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>菩提慧鱼是灵鱼一脉的14级材料，可用于对应层次的修真制作。</t>
+          <t>菩提慧鱼是灵鱼一脉的14级材料。</t>
         </is>
       </c>
       <c r="H239" s="3" t="n">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙鲲苗是灵鱼一脉的15级材料，可用于对应层次的修真制作。</t>
+          <t>鸿蒙鲲苗是灵鱼一脉的15级材料。</t>
         </is>
       </c>
       <c r="H240" s="3" t="n">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>太初神鲲是灵鱼一脉的16级材料，可用于对应层次的修真制作。</t>
+          <t>太初神鲲是灵鱼一脉的16级材料。</t>
         </is>
       </c>
       <c r="H241" s="3" t="n">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>清水灵珠是灵珠一脉的1级材料，可用于对应层次的修真制作。</t>
+          <t>清水灵珠是灵珠一脉的1级材料。</t>
         </is>
       </c>
       <c r="H242" s="3" t="n">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>青波珠是灵珠一脉的2级材料，可用于对应层次的修真制作。</t>
+          <t>青波珠是灵珠一脉的2级材料。</t>
         </is>
       </c>
       <c r="H243" s="3" t="n">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>赤潮珠是灵珠一脉的3级材料，可用于对应层次的修真制作。</t>
+          <t>赤潮珠是灵珠一脉的3级材料。</t>
         </is>
       </c>
       <c r="H244" s="3" t="n">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>月华珠是灵珠一脉的4级材料，可用于对应层次的修真制作。</t>
+          <t>月华珠是灵珠一脉的4级材料。</t>
         </is>
       </c>
       <c r="H245" s="3" t="n">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>雷鸣珠是灵珠一脉的5级材料，可用于对应层次的修真制作。</t>
+          <t>雷鸣珠是灵珠一脉的5级材料。</t>
         </is>
       </c>
       <c r="H246" s="3" t="n">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>玄冰珠是灵珠一脉的6级材料，可用于对应层次的修真制作。</t>
+          <t>玄冰珠是灵珠一脉的6级材料。</t>
         </is>
       </c>
       <c r="H247" s="3" t="n">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>地泉珠是灵珠一脉的7级材料，可用于对应层次的修真制作。</t>
+          <t>地泉珠是灵珠一脉的7级材料。</t>
         </is>
       </c>
       <c r="H248" s="3" t="n">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>星澜珠是灵珠一脉的8级材料，可用于对应层次的修真制作。</t>
+          <t>星澜珠是灵珠一脉的8级材料。</t>
         </is>
       </c>
       <c r="H249" s="3" t="n">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>龙涎珠是灵珠一脉的9级材料，可用于对应层次的修真制作。</t>
+          <t>龙涎珠是灵珠一脉的9级材料。</t>
         </is>
       </c>
       <c r="H250" s="3" t="n">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>凤泪珠是灵珠一脉的10级材料，可用于对应层次的修真制作。</t>
+          <t>凤泪珠是灵珠一脉的10级材料。</t>
         </is>
       </c>
       <c r="H251" s="3" t="n">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>九幽玄珠是灵珠一脉的11级材料，可用于对应层次的修真制作。</t>
+          <t>九幽玄珠是灵珠一脉的11级材料。</t>
         </is>
       </c>
       <c r="H252" s="3" t="n">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>扶桑日珠是灵珠一脉的12级材料，可用于对应层次的修真制作。</t>
+          <t>扶桑日珠是灵珠一脉的12级材料。</t>
         </is>
       </c>
       <c r="H253" s="3" t="n">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>建木碧珠是灵珠一脉的13级材料，可用于对应层次的修真制作。</t>
+          <t>建木碧珠是灵珠一脉的13级材料。</t>
         </is>
       </c>
       <c r="H254" s="3" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>菩提心珠是灵珠一脉的14级材料，可用于对应层次的修真制作。</t>
+          <t>菩提心珠是灵珠一脉的14级材料。</t>
         </is>
       </c>
       <c r="H255" s="3" t="n">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙源珠是灵珠一脉的15级材料，可用于对应层次的修真制作。</t>
+          <t>鸿蒙源珠是灵珠一脉的15级材料。</t>
         </is>
       </c>
       <c r="H256" s="3" t="n">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>太初神珠是灵珠一脉的16级材料，可用于对应层次的修真制作。</t>
+          <t>太初神珠是灵珠一脉的16级材料。</t>
         </is>
       </c>
       <c r="H257" s="3" t="n">
@@ -9489,11 +9489,11 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>青白玉是玉石一脉的1级材料，可用于对应层次的修真制作。</t>
+          <t>青白玉是玉石一脉的1级材料。</t>
         </is>
       </c>
       <c r="H258" s="3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I258" s="3" t="n">
         <v>3</v>
@@ -9524,11 +9524,11 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>云纹玉是玉石一脉的2级材料，可用于对应层次的修真制作。</t>
+          <t>云纹玉是玉石一脉的2级材料。</t>
         </is>
       </c>
       <c r="H259" s="3" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="I259" s="3" t="n">
         <v>10</v>
@@ -9559,11 +9559,11 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>赤霞玉是玉石一脉的3级材料，可用于对应层次的修真制作。</t>
+          <t>赤霞玉是玉石一脉的3级材料。</t>
         </is>
       </c>
       <c r="H260" s="3" t="n">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="I260" s="3" t="n">
         <v>25</v>
@@ -9594,11 +9594,11 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>月华玉是玉石一脉的4级材料，可用于对应层次的修真制作。</t>
+          <t>月华玉是玉石一脉的4级材料。</t>
         </is>
       </c>
       <c r="H261" s="3" t="n">
-        <v>279</v>
+        <v>58</v>
       </c>
       <c r="I261" s="3" t="n">
         <v>60</v>
@@ -9629,11 +9629,11 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>雷纹玉是玉石一脉的5级材料，可用于对应层次的修真制作。</t>
+          <t>雷纹玉是玉石一脉的5级材料。</t>
         </is>
       </c>
       <c r="H262" s="3" t="n">
-        <v>670</v>
+        <v>140</v>
       </c>
       <c r="I262" s="3" t="n">
         <v>140</v>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>玄冰玉是玉石一脉的6级材料，可用于对应层次的修真制作。</t>
+          <t>玄冰玉是玉石一脉的6级材料。</t>
         </is>
       </c>
       <c r="H263" s="3" t="n">
-        <v>1608</v>
+        <v>336</v>
       </c>
       <c r="I263" s="3" t="n">
         <v>300</v>
@@ -9699,11 +9699,11 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>地髓玉是玉石一脉的7级材料，可用于对应层次的修真制作。</t>
+          <t>地髓玉是玉石一脉的7级材料。</t>
         </is>
       </c>
       <c r="H264" s="3" t="n">
-        <v>3860</v>
+        <v>807</v>
       </c>
       <c r="I264" s="3" t="n">
         <v>700</v>
@@ -9734,11 +9734,11 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>星辉玉是玉石一脉的8级材料，可用于对应层次的修真制作。</t>
+          <t>星辉玉是玉石一脉的8级材料。</t>
         </is>
       </c>
       <c r="H265" s="3" t="n">
-        <v>9264</v>
+        <v>1937</v>
       </c>
       <c r="I265" s="3" t="n">
         <v>1500</v>
@@ -9769,11 +9769,11 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>龙血玉是玉石一脉的9级材料，可用于对应层次的修真制作。</t>
+          <t>龙血玉是玉石一脉的9级材料。</t>
         </is>
       </c>
       <c r="H266" s="3" t="n">
-        <v>22234</v>
+        <v>4649</v>
       </c>
       <c r="I266" s="3" t="n">
         <v>3500</v>
@@ -9804,11 +9804,11 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>凤栖玉是玉石一脉的10级材料，可用于对应层次的修真制作。</t>
+          <t>凤栖玉是玉石一脉的10级材料。</t>
         </is>
       </c>
       <c r="H267" s="3" t="n">
-        <v>53362</v>
+        <v>11158</v>
       </c>
       <c r="I267" s="3" t="n">
         <v>8000</v>
@@ -9839,11 +9839,11 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>九幽玄玉是玉石一脉的11级材料，可用于对应层次的修真制作。</t>
+          <t>九幽玄玉是玉石一脉的11级材料。</t>
         </is>
       </c>
       <c r="H268" s="3" t="n">
-        <v>128069</v>
+        <v>26780</v>
       </c>
       <c r="I268" s="3" t="n">
         <v>18000</v>
@@ -9874,11 +9874,11 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>扶桑阳玉是玉石一脉的12级材料，可用于对应层次的修真制作。</t>
+          <t>扶桑阳玉是玉石一脉的12级材料。</t>
         </is>
       </c>
       <c r="H269" s="3" t="n">
-        <v>307366</v>
+        <v>64272</v>
       </c>
       <c r="I269" s="3" t="n">
         <v>40000</v>
@@ -9909,11 +9909,11 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>建木碧玉是玉石一脉的13级材料，可用于对应层次的修真制作。</t>
+          <t>建木碧玉是玉石一脉的13级材料。</t>
         </is>
       </c>
       <c r="H270" s="3" t="n">
-        <v>737679</v>
+        <v>154253</v>
       </c>
       <c r="I270" s="3" t="n">
         <v>90000</v>
@@ -9944,11 +9944,11 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>菩提心玉是玉石一脉的14级材料，可用于对应层次的修真制作。</t>
+          <t>菩提心玉是玉石一脉的14级材料。</t>
         </is>
       </c>
       <c r="H271" s="3" t="n">
-        <v>1770430</v>
+        <v>370208</v>
       </c>
       <c r="I271" s="3" t="n">
         <v>200000</v>
@@ -9979,11 +9979,11 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙源玉是玉石一脉的15级材料，可用于对应层次的修真制作。</t>
+          <t>鸿蒙源玉是玉石一脉的15级材料。</t>
         </is>
       </c>
       <c r="H272" s="3" t="n">
-        <v>4249032</v>
+        <v>888500</v>
       </c>
       <c r="I272" s="3" t="n">
         <v>450000</v>
@@ -10014,11 +10014,11 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>太初神玉是玉石一脉的16级材料，可用于对应层次的修真制作。</t>
+          <t>太初神玉是玉石一脉的16级材料。</t>
         </is>
       </c>
       <c r="H273" s="3" t="n">
-        <v>10197677</v>
+        <v>2132400</v>
       </c>
       <c r="I273" s="3" t="n">
         <v>1000000</v>
@@ -15138,7 +15138,7 @@
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H149" s="3" t="n">
         <v>5</v>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>松露养元散以松露灵脂、青鳞灵鱼、雾芽草合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>松露养元散以松露灵脂、青鳞灵鱼、雾芽草合炼而成，丹药灵韵层次分明。</t>
         </is>
       </c>
       <c r="G209" s="3" t="n">
@@ -17336,7 +17336,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>银鳞抱元丸以银须鲫、青络花合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>银鳞抱元丸以银须鲫、青络花合炼而成，丹药灵韵层次分明。</t>
         </is>
       </c>
       <c r="G210" s="3" t="n">
@@ -17370,7 +17370,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>月桂玉露丹以月桂凝脂、月纹鳜、玉壶露合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>月桂玉露丹以月桂凝脂、月纹鳜、玉壶露合炼而成，丹药灵韵层次分明。</t>
         </is>
       </c>
       <c r="G211" s="3" t="n">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>雷脂雪魄丸以桃木雷脂、雷鳍鲶、雪魄莲合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>雷脂雪魄丸以桃木雷脂、雷鳍鲶、雪魄莲合炼而成，丹药灵韵层次分明。</t>
         </is>
       </c>
       <c r="G212" s="3" t="n">
@@ -17438,7 +17438,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>沉香青冥丹以沉香地髓、地脉鳅、苍梧藤合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>沉香青冥丹以沉香地髓、地脉鳅、苍梧藤合炼而成，丹药灵韵层次分明。</t>
         </is>
       </c>
       <c r="G213" s="3" t="n">
@@ -17472,7 +17472,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>星脂霆元丹以紫檀星脂、星斑鲷、霆光竹合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>星脂霆元丹以紫檀星脂、星斑鲷、霆光竹合炼而成，丹药灵韵层次分明。</t>
         </is>
       </c>
       <c r="G214" s="3" t="n">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>凤鲤星华丹以凤栖香脂、凤尾锦鲤、星坠蕊合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>凤鲤星华丹以凤栖香脂、凤尾锦鲤、星坠蕊合炼而成，丹药灵韵层次分明。</t>
         </is>
       </c>
       <c r="G215" s="3" t="n">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>扶桑九转丹以扶桑日脂、扶桑金鲤、九曲槲合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>扶桑九转丹以扶桑日脂、扶桑金鲤、九曲槲合炼而成，丹药灵韵层次分明。</t>
         </is>
       </c>
       <c r="G216" s="3" t="n">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>菩提龙元丹以菩提心脂、菩提慧鱼、螭涎兰合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>菩提龙元丹以菩提心脂、菩提慧鱼、螭涎兰合炼而成，丹药灵韵层次分明。</t>
         </is>
       </c>
       <c r="G217" s="3" t="n">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>太初造化丹以太初神脂、太初神鲲、太初道种合炼而成，丹药灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>太初造化丹以太初神脂、太初神鲲、太初道种合炼而成，丹药灵韵层次分明。</t>
         </is>
       </c>
       <c r="G218" s="3" t="n">
@@ -17642,7 +17642,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>松露青果酿以松露灵脂、山青果合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>松露青果酿以松露灵脂、山青果合炼而成，灵酒灵韵层次分明。</t>
         </is>
       </c>
       <c r="G219" s="3" t="n">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>银须青禾酒以银须鲫、青禾米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>银须青禾酒以银须鲫、青禾米合炼而成，灵酒灵韵层次分明。</t>
         </is>
       </c>
       <c r="G220" s="3" t="n">
@@ -17710,7 +17710,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>赤枫金铃酿以赤枫脂、赤尾鲤、金铃果合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>赤枫金铃酿以赤枫脂、赤尾鲤、金铃果合炼而成，灵酒灵韵层次分明。</t>
         </is>
       </c>
       <c r="G221" s="3" t="n">
@@ -17744,7 +17744,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>雷脂雪纹酒以桃木雷脂、雷鳍鲶、雪纹米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>雷脂雪纹酒以桃木雷脂、雷鳍鲶、雪纹米合炼而成，灵酒灵韵层次分明。</t>
         </is>
       </c>
       <c r="G222" s="3" t="n">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>冰魄苍梧酿以冰梧寒脂、冰魄鲑、苍梧子合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>冰魄苍梧酿以冰梧寒脂、冰魄鲑、苍梧子合炼而成，灵酒灵韵层次分明。</t>
         </is>
       </c>
       <c r="G223" s="3" t="n">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>星脂雷芒酒以紫檀星脂、星斑鲷、雷芒米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>星脂雷芒酒以紫檀星脂、星斑鲷、雷芒米合炼而成，灵酒灵韵层次分明。</t>
         </is>
       </c>
       <c r="G224" s="3" t="n">
@@ -17846,7 +17846,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>龙血星子酿以龙血木脂、龙须鲤、星子米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>龙血星子酿以龙血木脂、龙须鲤、星子米合炼而成，灵酒灵韵层次分明。</t>
         </is>
       </c>
       <c r="G225" s="3" t="n">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>九幽九曲醪以九幽玄脂、九幽玄鱼、九曲米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>九幽九曲醪以九幽玄脂、九幽玄鱼、九曲米合炼而成，灵酒灵韵层次分明。</t>
         </is>
       </c>
       <c r="G226" s="3" t="n">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>建木龙牙酿以建木玉脂、建木游龙、龙牙米合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>建木龙牙酿以建木玉脂、建木游龙、龙牙米合炼而成，灵酒灵韵层次分明。</t>
         </is>
       </c>
       <c r="G227" s="3" t="n">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙玄粟酒以鸿蒙源脂、鸿蒙鲲苗、太初玄粟合炼而成，灵酒灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>鸿蒙玄粟酒以鸿蒙源脂、鸿蒙鲲苗、太初玄粟合炼而成，灵酒灵韵层次分明。</t>
         </is>
       </c>
       <c r="G228" s="3" t="n">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>青枝铜骨剑以青灵枝、赤髓铜合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>青枝铜骨剑以青灵枝、赤髓铜合炼而成，锻造灵韵层次分明。</t>
         </is>
       </c>
       <c r="G229" s="3" t="n">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>云木乌铁刀以云纹木、乌纹铁合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>云木乌铁刀以云纹木、乌纹铁合炼而成，锻造灵韵层次分明。</t>
         </is>
       </c>
       <c r="G230" s="3" t="n">
@@ -18050,7 +18050,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>月桂白金杖以月桂灵木、月华玉、太白金母合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>月桂白金杖以月桂灵木、月华玉、太白金母合炼而成，锻造灵韵层次分明。</t>
         </is>
       </c>
       <c r="G231" s="3" t="n">
@@ -18084,7 +18084,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>雷木玄冰枪以雷击桃木、雷纹玉、玄冰陨铁合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>雷木玄冰枪以雷击桃木、雷纹玉、玄冰陨铁合炼而成，锻造灵韵层次分明。</t>
         </is>
       </c>
       <c r="G232" s="3" t="n">
@@ -18118,7 +18118,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>沉香青罡印以地脉沉香、地髓玉、青罡玉合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>沉香青罡印以地脉沉香、地髓玉、青罡玉合炼而成，锻造灵韵层次分明。</t>
         </is>
       </c>
       <c r="G233" s="3" t="n">
@@ -18152,7 +18152,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>紫檀雷极轮以星辉紫檀、星辉玉、雷极砂合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>紫檀雷极轮以星辉紫檀、星辉玉、雷极砂合炼而成，锻造灵韵层次分明。</t>
         </is>
       </c>
       <c r="G234" s="3" t="n">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>凤木星陨弓以凤栖神木、凤栖玉、星陨铁核合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>凤木星陨弓以凤栖神木、凤栖玉、星陨铁核合炼而成，锻造灵韵层次分明。</t>
         </is>
       </c>
       <c r="G235" s="3" t="n">
@@ -18220,7 +18220,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>扶桑九幽戟以扶桑阳木、扶桑阳玉、九幽沉铁合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>扶桑九幽戟以扶桑阳木、扶桑阳玉、九幽沉铁合炼而成，锻造灵韵层次分明。</t>
         </is>
       </c>
       <c r="G236" s="3" t="n">
@@ -18254,7 +18254,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>菩提月魄钟以菩提道木、菩提心玉、月魄寒玉合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>菩提月魄钟以菩提道木、菩提心玉、月魄寒玉合炼而成，锻造灵韵层次分明。</t>
         </is>
       </c>
       <c r="G237" s="3" t="n">
@@ -18288,7 +18288,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>世界树开天斧以世界树心、太初神玉、鸿蒙母晶合炼而成，锻造灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>世界树开天斧以世界树心、太初神玉、鸿蒙母晶合炼而成，锻造灵韵层次分明。</t>
         </is>
       </c>
       <c r="G238" s="3" t="n">
@@ -18322,7 +18322,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>清珠岚障阵以清水灵珠、青白玉、清岚障图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>清珠岚障阵以清水灵珠、青白玉、清岚障图合炼而成，阵法灵韵层次分明。</t>
         </is>
       </c>
       <c r="G239" s="3" t="n">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>云玉聚炁阵以青波珠、云纹玉、引星聚炁图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>云玉聚炁阵以青波珠、云纹玉、引星聚炁图合炼而成，阵法灵韵层次分明。</t>
         </is>
       </c>
       <c r="G240" s="3" t="n">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>月珠锁灵阵以赤潮珠、月华珠、赤霞玉、三垣锁灵图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>月珠锁灵阵以赤潮珠、月华珠、赤霞玉、三垣锁灵图合炼而成，阵法灵韵层次分明。</t>
         </is>
       </c>
       <c r="G241" s="3" t="n">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>雷珠寒光阵以雷鸣珠、雷纹玉、四渎寒图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>雷珠寒光阵以雷鸣珠、雷纹玉、四渎寒图合炼而成，阵法灵韵层次分明。</t>
         </is>
       </c>
       <c r="G242" s="3" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>地珠载岳阵以玄冰珠、地泉珠、玄冰玉、玄龟载岳图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>地珠载岳阵以玄冰珠、地泉珠、玄冰玉、玄龟载岳图合炼而成，阵法灵韵层次分明。</t>
         </is>
       </c>
       <c r="G243" s="3" t="n">
@@ -18492,7 +18492,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>星珠九霄阵以星澜珠、星辉玉、九霄雷篆图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>星珠九霄阵以星澜珠、星辉玉、九霄雷篆图合炼而成，阵法灵韵层次分明。</t>
         </is>
       </c>
       <c r="G244" s="3" t="n">
@@ -18526,7 +18526,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>凤珠星罗阵以龙涎珠、凤泪珠、龙血玉、星罗天盘图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>凤珠星罗阵以龙涎珠、凤泪珠、龙血玉、星罗天盘图合炼而成，阵法灵韵层次分明。</t>
         </is>
       </c>
       <c r="G245" s="3" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>日珠续命阵以九幽玄珠、扶桑日珠、九幽玄玉、九幽续命图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>日珠续命阵以九幽玄珠、扶桑日珠、九幽玄玉、九幽续命图合炼而成，阵法灵韵层次分明。</t>
         </is>
       </c>
       <c r="G246" s="3" t="n">
@@ -18594,7 +18594,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>心珠御龙阵以建木碧珠、菩提心珠、建木碧玉、苍龙御天图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>心珠御龙阵以建木碧珠、菩提心珠、建木碧玉、苍龙御天图合炼而成，阵法灵韵层次分明。</t>
         </is>
       </c>
       <c r="G247" s="3" t="n">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>太初万象阵以鸿蒙源珠、太初神珠、鸿蒙源玉、太一归元图合炼而成，阵法灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>太初万象阵以鸿蒙源珠、太初神珠、鸿蒙源玉、太一归元图合炼而成，阵法灵韵层次分明。</t>
         </is>
       </c>
       <c r="G248" s="3" t="n">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>青枝镇煞符以青灵枝、山豕血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>青枝镇煞符以青灵枝、山豕血合炼而成，符箓灵韵层次分明。</t>
         </is>
       </c>
       <c r="G249" s="3" t="n">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>青檀净心符以青檀脂、云鹿灵血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>青檀净心符以青檀脂、云鹿灵血合炼而成，符箓灵韵层次分明。</t>
         </is>
       </c>
       <c r="G250" s="3" t="n">
@@ -18730,7 +18730,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>赤霞金身符以赤霞杉、月桂凝脂、金蟾髓合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>赤霞金身符以赤霞杉、月桂凝脂、金蟾髓合炼而成，符箓灵韵层次分明。</t>
         </is>
       </c>
       <c r="G251" s="3" t="n">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>雷木寒霜符以雷击桃木、桃木雷脂、冰蛇寒血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>雷木寒霜符以雷击桃木、桃木雷脂、冰蛇寒血合炼而成，符箓灵韵层次分明。</t>
         </is>
       </c>
       <c r="G252" s="3" t="n">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>冰梧青鸾符以玄冰梧桐、沉香地髓、青鸾碧血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>冰梧青鸾符以玄冰梧桐、沉香地髓、青鸾碧血合炼而成，符箓灵韵层次分明。</t>
         </is>
       </c>
       <c r="G253" s="3" t="n">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>紫檀雷鹏符以星辉紫檀、紫檀星脂、雷鹏紫血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>紫檀雷鹏符以星辉紫檀、紫檀星脂、雷鹏紫血合炼而成，符箓灵韵层次分明。</t>
         </is>
       </c>
       <c r="G254" s="3" t="n">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>龙血星狼符以龙血古木、凤栖香脂、星狼银血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>龙血星狼符以龙血古木、凤栖香脂、星狼银血合炼而成，符箓灵韵层次分明。</t>
         </is>
       </c>
       <c r="G255" s="3" t="n">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>九幽九命符以九幽冥木、扶桑日脂、九命猫血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>九幽九命符以九幽冥木、扶桑日脂、九命猫血合炼而成，符箓灵韵层次分明。</t>
         </is>
       </c>
       <c r="G256" s="3" t="n">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>建木龙血符以建木灵芯、菩提心脂、苍龙真血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>建木龙血符以建木灵芯、菩提心脂、苍龙真血合炼而成，符箓灵韵层次分明。</t>
         </is>
       </c>
       <c r="G257" s="3" t="n">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙太古符以鸿蒙祖木、太初神脂、太古源血合炼而成，符箓灵韵层次分明，可用于对应境界的订单与制作循环。</t>
+          <t>鸿蒙太古符以鸿蒙祖木、太初神脂、太古源血合炼而成，符箓灵韵层次分明。</t>
         </is>
       </c>
       <c r="G258" s="3" t="n">
@@ -23580,13 +23580,13 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>浅砂矿口以河砂与碎岩筑成，矿壁留有新凿出的浅痕，并有小概率产出玉石。</t>
+          <t>浅砂矿口以河砂与碎岩筑成，矿壁留有新凿出的浅痕，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr"/>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2001:665;4001:285;1501:50</t>
+          <t>2001:500;4001:250;1501:250</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr"/>
@@ -23624,13 +23624,13 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>乌铁矿井立于溪谷缓坡，井下回声沉闷如钟，并有小概率产出玉石。</t>
+          <t>乌铁矿井立于溪谷缓坡，井下回声沉闷如钟，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>2001:652;4001:279;2002:13;4002:6;1501:49;1502:1</t>
+          <t>2001:490;4001:245;2002:10;4002:5;1501:245;1502:5</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr"/>
@@ -23668,13 +23668,13 @@
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>匠人取月银石柱建成月银矿洞，洞顶在月夜泛出银辉，并有小概率产出玉石。</t>
+          <t>匠人取月银石柱建成月银矿洞，洞顶在月夜泛出银辉，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2001:638;4001:274;2002:27;4002:11;1501:48;1502:2</t>
+          <t>2001:480;4001:240;2002:20;4002:10;1501:240;1502:10</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr"/>
@@ -23712,13 +23712,13 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>传闻白金矿脉旧址在云崖石台，金脉沿岩层纵横生长，并有小概率产出玉石。</t>
+          <t>传闻白金矿脉旧址在云崖石台，金脉沿岩层纵横生长，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>2001:625;4001:268;2002:40;4002:17;1501:47;1502:3</t>
+          <t>2001:470;4001:235;2002:30;4002:15;1501:235;1502:15</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr"/>
@@ -23756,13 +23756,13 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>寒谷背阴处所见的冰陨深井由冰陨石与寒木构成，井口吐出的风带着冰屑，并有小概率产出玉石。</t>
+          <t>寒谷背阴处所见的冰陨深井由冰陨石与寒木构成，井口吐出的风带着冰屑，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2001:612;4001:262;2002:53;4002:23;1501:46;1502:4</t>
+          <t>2001:460;4001:230;2002:40;4002:20;1501:230;1502:20</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr"/>
@@ -23800,13 +23800,13 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>地火晶窟以地火岩与赤铜筑成，晶窟深处常有红光跃动，并有小概率产出玉石。</t>
+          <t>地火晶窟以地火岩与赤铜筑成，晶窟深处常有红光跃动，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2001:605;4001:259;2002:60;4002:26;1501:46;1502:4</t>
+          <t>2001:455;4001:227;2002:45;4002:23;1501:230;1502:20</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr"/>
@@ -23844,13 +23844,13 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>青罡玉坑立于苍梧秘境，玉壁内云纹缓缓迁移，并有小概率产出玉石。</t>
+          <t>青罡玉坑立于苍梧秘境，玉壁内云纹缓缓迁移，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2001:599;4001:257;2002:66;4002:28;1501:45;1502:5</t>
+          <t>2001:450;4001:225;2002:50;4002:25;1501:225;1502:25</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -23888,13 +23888,13 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>匠人取雷极砂砖建成雷极砂场，砂层摩擦时传来细雷，并有小概率产出玉石。</t>
+          <t>匠人取雷极砂砖建成雷极砂场，砂层摩擦时传来细雷，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>2001:572;4001:245;2002:80;4002:34;2003:13;4003:6;1501:43;1502:6;1503:1</t>
+          <t>2001:430;4001:215;2002:60;4002:30;2003:10;4003:5;1501:215;1502:30;1503:5</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr"/>
@@ -23932,13 +23932,13 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>传闻坤髓矿府旧址在坤元地脉，地脉气息沿矿壁缓缓升起，并有小概率产出玉石。</t>
+          <t>传闻坤髓矿府旧址在坤元地脉，地脉气息沿矿壁缓缓升起，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2001:545;4001:234;2002:100;4002:43;2003:20;4003:8;1501:41;1502:8;1503:1</t>
+          <t>2001:410;4001:205;2002:75;4002:38;2003:15;4003:7;1501:205;1502:40;1503:5</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -23976,13 +23976,13 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>星落天原所见的星陨矿坑由星陨铁与天河砂构成，夜间矿壁会映出群星轨迹，并有小概率产出玉石。</t>
+          <t>星落天原所见的星陨矿坑由星陨铁与天河砂构成，夜间矿壁会映出群星轨迹，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>2001:505;4001:217;2002:133;4002:57;2003:27;4003:11;1501:38;1502:10;1503:2</t>
+          <t>2001:380;4001:190;2002:100;4002:50;2003:20;4003:10;1501:190;1502:50;1503:10</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr"/>
@@ -24020,13 +24020,13 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>太虚玉窟以紫府玉与烟霞木筑成，紫色云烟常在矿壁周围盘旋，并有小概率产出玉石。</t>
+          <t>太虚玉窟以紫府玉与烟霞木筑成，紫色云烟常在矿壁周围盘旋，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2001:466;4001:200;2002:166;4002:71;2003:33;4003:14;1501:35;1502:13;1503:2</t>
+          <t>2001:350;4001:176;2002:125;4002:62;2003:25;4003:12;1501:175;1502:65;1503:10</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -24064,13 +24064,13 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>九幽铁渊立于九曲地宫，矿壁依九曲方位层层展开，并有小概率产出玉石。</t>
+          <t>九幽铁渊立于九曲地宫，矿壁依九曲方位层层展开，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>2001:439;4001:188;2002:173;4002:74;2003:46;4003:20;2004:7;4004:3;1501:33;1502:13;1503:4</t>
+          <t>2001:330;4001:165;2002:130;4002:65;2003:35;4003:17;2004:5;4004:3;1501:165;1502:65;1503:20</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr"/>
@@ -24108,13 +24108,13 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>匠人取涅火晶与赤金建成日精金脉，赤金纹路随天火明灭不定，并有小概率产出玉石。</t>
+          <t>匠人取涅火晶与赤金建成日精金脉，赤金纹路随天火明灭不定，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2001:412;4001:177;2002:179;4002:77;2003:60;4003:26;2004:13;4004:6;1501:31;1502:14;1503:4;1504:1</t>
+          <t>2001:310;4001:155;2002:135;4002:67;2003:45;4003:23;2004:10;4004:5;1501:155;1502:70;1503:20;1504:5</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -24152,13 +24152,13 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>传闻月魄玉山旧址在龙眠古渊，矿壁上隐约盘着龙形云气，并有小概率产出玉石。</t>
+          <t>传闻月魄玉山旧址在龙眠古渊，矿壁上隐约盘着龙形云气，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>2001:386;4001:165;2002:186;4002:80;2003:73;4003:31;2004:20;4004:9;1501:29;1502:14;1503:6;1504:1</t>
+          <t>2001:290;4001:145;2002:140;4002:70;2003:55;4003:27;2004:15;4004:8;1501:145;1502:70;1503:30;1504:5</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr"/>
@@ -24196,13 +24196,13 @@
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>凤栖神木所见的天河砂海由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过，并有小概率产出玉石。</t>
+          <t>凤栖神木所见的天河砂海由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr"/>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2001:359;4001:154;2002:193;4002:83;2003:86;4003:37;2004:27;4004:11;1501:27;1502:15;1503:6;1504:2</t>
+          <t>2001:270;4001:135;2002:145;4002:73;2003:65;4003:32;2004:20;4004:10;1501:135;1502:75;1503:30;1504:10</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -24240,13 +24240,13 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙晶域以太初晶与鸿蒙母金筑成，近看矿壁仿佛隔着太初雾海，并有小概率产出玉石。</t>
+          <t>鸿蒙晶域以太初晶与鸿蒙母金筑成，近看矿壁仿佛隔着太初雾海，并有四分之一概率产出玉石。</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr"/>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>2001:333;4001:143;2002:199;4002:85;2003:100;4003:43;2004:33;4004:14;1501:25;1502:15;1503:8;1504:2</t>
+          <t>2001:250;4001:125;2002:150;4002:75;2003:75;4003:38;2004:25;4004:12;1501:125;1502:75;1503:40;1504:10</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr"/>

--- a/config/xlsx/items.xlsx
+++ b/config/xlsx/items.xlsx
@@ -18991,7 +18991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19582,7 +19582,7 @@
         <v>28001</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>28002</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>28003</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
       </c>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
       </c>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
       </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
       </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
       </c>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -20639,6 +20639,141 @@
       </c>
       <c r="I48" s="3" t="n">
         <v>40</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n" s="2">
+        <v>1701</v>
+      </c>
+      <c r="B49" t="n" s="2">
+        <v>1</v>
+      </c>
+      <c r="C49" t="str" s="3">
+        <v>1星卡包</v>
+      </c>
+      <c r="D49" t="str" s="3">
+        <v>res://assets/items/card_pack.svg</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" t="n" s="3">
+        <v>5</v>
+      </c>
+      <c r="G49" t="str" s="3">
+        <v>在物品暂存区开启，保底获得一张1星卡片。</v>
+      </c>
+      <c r="H49" t="n" s="3">
+        <v>9</v>
+      </c>
+      <c r="I49" t="n" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n" s="2">
+        <v>1702</v>
+      </c>
+      <c r="B50" t="n" s="2">
+        <v>2</v>
+      </c>
+      <c r="C50" t="str" s="3">
+        <v>2星卡包</v>
+      </c>
+      <c r="D50" t="str" s="3">
+        <v>res://assets/items/card_pack.svg</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" t="n" s="3">
+        <v>5</v>
+      </c>
+      <c r="G50" t="str" s="3">
+        <v>在物品暂存区开启，保底获得一张2星卡片。</v>
+      </c>
+      <c r="H50" t="n" s="3">
+        <v>9</v>
+      </c>
+      <c r="I50" t="n" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n" s="2">
+        <v>1703</v>
+      </c>
+      <c r="B51" t="n" s="2">
+        <v>3</v>
+      </c>
+      <c r="C51" t="str" s="3">
+        <v>3星卡包</v>
+      </c>
+      <c r="D51" t="str" s="3">
+        <v>res://assets/items/card_pack.svg</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" t="n" s="3">
+        <v>5</v>
+      </c>
+      <c r="G51" t="str" s="3">
+        <v>在物品暂存区开启，保底获得一张3星卡片。</v>
+      </c>
+      <c r="H51" t="n" s="3">
+        <v>9</v>
+      </c>
+      <c r="I51" t="n" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n" s="2">
+        <v>1704</v>
+      </c>
+      <c r="B52" t="n" s="2">
+        <v>4</v>
+      </c>
+      <c r="C52" t="str" s="3">
+        <v>4星卡包</v>
+      </c>
+      <c r="D52" t="str" s="3">
+        <v>res://assets/items/card_pack.svg</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" t="n" s="3">
+        <v>5</v>
+      </c>
+      <c r="G52" t="str" s="3">
+        <v>在物品暂存区开启，保底获得一张4星卡片。</v>
+      </c>
+      <c r="H52" t="n" s="3">
+        <v>9</v>
+      </c>
+      <c r="I52" t="n" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n" s="2">
+        <v>1705</v>
+      </c>
+      <c r="B53" t="n" s="2">
+        <v>5</v>
+      </c>
+      <c r="C53" t="str" s="3">
+        <v>5星卡包</v>
+      </c>
+      <c r="D53" t="str" s="3">
+        <v>res://assets/items/card_pack.svg</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" t="n" s="3">
+        <v>5</v>
+      </c>
+      <c r="G53" t="str" s="3">
+        <v>在物品暂存区开启，保底获得一张5星卡片。</v>
+      </c>
+      <c r="H53" t="n" s="3">
+        <v>9</v>
+      </c>
+      <c r="I53" t="n" s="3">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/config/xlsx/items.xlsx
+++ b/config/xlsx/items.xlsx
@@ -7249,7 +7249,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>青灵枝是灵木一脉的1级材料。</t>
+          <t>青灵枝生于青篱灵田，枝梢泛着清润青光。</t>
         </is>
       </c>
       <c r="H194" s="3" t="n">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>云纹木是灵木一脉的2级材料。</t>
+          <t>云纹木木纹如云，折面隐约流转浅白纹路。</t>
         </is>
       </c>
       <c r="H195" s="3" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>赤霞杉是灵木一脉的3级材料。</t>
+          <t>赤霞杉树脂带着赤霞，针叶间常有暖光。</t>
         </is>
       </c>
       <c r="H196" s="3" t="n">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>月桂灵木是灵木一脉的4级材料。</t>
+          <t>月桂灵木桂香清冷，木心映着淡淡月华。</t>
         </is>
       </c>
       <c r="H197" s="3" t="n">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>雷击桃木是灵木一脉的5级材料。</t>
+          <t>雷击桃木经雷火淬过，纹理间残留细碎电芒。</t>
         </is>
       </c>
       <c r="H198" s="3" t="n">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>玄冰梧桐是灵木一脉的6级材料。</t>
+          <t>玄冰梧桐枝干覆着薄霜，触之寒意直入掌心。</t>
         </is>
       </c>
       <c r="H199" s="3" t="n">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>地脉沉香是灵木一脉的7级材料。</t>
+          <t>地脉沉香根系扎入地脉，木屑散出厚重土息。</t>
         </is>
       </c>
       <c r="H200" s="3" t="n">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>星辉紫檀是灵木一脉的8级材料。</t>
+          <t>星辉紫檀木色深紫，年轮间点缀着星辉。</t>
         </is>
       </c>
       <c r="H201" s="3" t="n">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>龙血古木是灵木一脉的9级材料。</t>
+          <t>龙血古木树心凝着龙血般的赤纹，久置不褪。</t>
         </is>
       </c>
       <c r="H202" s="3" t="n">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>凤栖神木是灵木一脉的10级材料。</t>
+          <t>凤栖神木枝叶舒展如凤羽，木香中带着暖霞。</t>
         </is>
       </c>
       <c r="H203" s="3" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>九幽冥木是灵木一脉的11级材料。</t>
+          <t>九幽冥木色泽幽黑，断面浮起九道暗纹。</t>
         </is>
       </c>
       <c r="H204" s="3" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>扶桑阳木是灵木一脉的12级材料。</t>
+          <t>扶桑阳木木心温热，日光下透出金红光泽。</t>
         </is>
       </c>
       <c r="H205" s="3" t="n">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>建木灵芯是灵木一脉的13级材料。</t>
+          <t>建木灵芯藏于古木深处，青金色木炁缓缓流动。</t>
         </is>
       </c>
       <c r="H206" s="3" t="n">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>菩提道木是灵木一脉的14级材料。</t>
+          <t>菩提道木枝节天然结成道纹，靠近时心神清明。</t>
         </is>
       </c>
       <c r="H207" s="3" t="n">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙祖木是灵木一脉的15级材料。</t>
+          <t>鸿蒙祖木木质厚重，树纹间交织着清浊二气。</t>
         </is>
       </c>
       <c r="H208" s="3" t="n">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>世界树心是灵木一脉的16级材料。</t>
+          <t>世界树心晶莹如琥珀，内部仿佛容纳万象枝脉。</t>
         </is>
       </c>
       <c r="H209" s="3" t="n">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>松露灵脂是灵脂一脉的1级材料。</t>
+          <t>松露灵脂凝自松根露珠，清香中带着山野湿气。</t>
         </is>
       </c>
       <c r="H210" s="3" t="n">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>青檀脂是灵脂一脉的2级材料。</t>
+          <t>青檀脂色泽青润，轻触便有檀香萦绕。</t>
         </is>
       </c>
       <c r="H211" s="3" t="n">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>赤枫脂是灵脂一脉的3级材料。</t>
+          <t>赤枫脂如融化的晚霞，温热时泛起红光。</t>
         </is>
       </c>
       <c r="H212" s="3" t="n">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>月桂凝脂是灵脂一脉的4级材料。</t>
+          <t>月桂凝脂清凉细腻，表面映着一层月白。</t>
         </is>
       </c>
       <c r="H213" s="3" t="n">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>桃木雷脂是灵脂一脉的5级材料。</t>
+          <t>桃木雷脂带着桃木清香，偶尔迸出细小电花。</t>
         </is>
       </c>
       <c r="H214" s="3" t="n">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>冰梧寒脂是灵脂一脉的6级材料。</t>
+          <t>冰梧寒脂脂体寒凝如冰，瓶壁常结薄霜。</t>
         </is>
       </c>
       <c r="H215" s="3" t="n">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>沉香地髓是灵脂一脉的7级材料。</t>
+          <t>沉香地髓浓稠沉静，散发沉香与土脉气息。</t>
         </is>
       </c>
       <c r="H216" s="3" t="n">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>紫檀星脂是灵脂一脉的8级材料。</t>
+          <t>紫檀星脂色深如夜，星点在其中缓缓游动。</t>
         </is>
       </c>
       <c r="H217" s="3" t="n">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>龙血木脂是灵脂一脉的9级材料。</t>
+          <t>龙血木脂色泽赤红，凝结后宛如一滴龙血。</t>
         </is>
       </c>
       <c r="H218" s="3" t="n">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>凤栖香脂是灵脂一脉的10级材料。</t>
+          <t>凤栖香脂香气暖润，流动时映出凤羽般的金光。</t>
         </is>
       </c>
       <c r="H219" s="3" t="n">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>九幽玄脂是灵脂一脉的11级材料。</t>
+          <t>九幽玄脂幽暗深沉，光照下隐约可见九重纹理。</t>
         </is>
       </c>
       <c r="H220" s="3" t="n">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>扶桑日脂是灵脂一脉的12级材料。</t>
+          <t>扶桑日脂温烈，表面常浮着金色火纹。</t>
         </is>
       </c>
       <c r="H221" s="3" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>建木玉脂是灵脂一脉的13级材料。</t>
+          <t>建木玉脂清透，内里有木纹般的青影。</t>
         </is>
       </c>
       <c r="H222" s="3" t="n">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>菩提心脂是灵脂一脉的14级材料。</t>
+          <t>菩提心脂澄澈宁静，靠近时能闻到淡淡檀香。</t>
         </is>
       </c>
       <c r="H223" s="3" t="n">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙源脂是灵脂一脉的15级材料。</t>
+          <t>鸿蒙源脂分呈清浊二色，彼此交缠不散。</t>
         </is>
       </c>
       <c r="H224" s="3" t="n">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>太初神脂是灵脂一脉的16级材料。</t>
+          <t>太初神脂厚重温润，表面浮着天地初开的微光。</t>
         </is>
       </c>
       <c r="H225" s="3" t="n">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>青鳞灵鱼是灵鱼一脉的1级材料。</t>
+          <t>青鳞灵鱼鳞片青亮，游动时拖出一线灵光。</t>
         </is>
       </c>
       <c r="H226" s="3" t="n">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>银须鲫是灵鱼一脉的2级材料。</t>
+          <t>银须鲫须发如银，鳞面映着细碎水光。</t>
         </is>
       </c>
       <c r="H227" s="3" t="n">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>赤尾鲤是灵鱼一脉的3级材料。</t>
+          <t>赤尾鲤尾鳍赤红，跃出水面时仿佛带起霞火。</t>
         </is>
       </c>
       <c r="H228" s="3" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>月纹鳜是灵鱼一脉的4级材料。</t>
+          <t>月纹鳜鱼身月纹清晰，夜间会泛出柔和白光。</t>
         </is>
       </c>
       <c r="H229" s="3" t="n">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>雷鳍鲶是灵鱼一脉的5级材料。</t>
+          <t>雷鳍鲶背鳍藏有雷纹，摆尾时水面传来细微震响。</t>
         </is>
       </c>
       <c r="H230" s="3" t="n">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>冰魄鲑是灵鱼一脉的6级材料。</t>
+          <t>冰魄鲑鱼鳞透白如冰，周身常绕着寒雾。</t>
         </is>
       </c>
       <c r="H231" s="3" t="n">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>地脉鳅是灵鱼一脉的7级材料。</t>
+          <t>地脉鳅身形细长，鳞下隐有土黄色地脉纹。</t>
         </is>
       </c>
       <c r="H232" s="3" t="n">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>星斑鲷是灵鱼一脉的8级材料。</t>
+          <t>星斑鲷通体银蓝，斑点如夜空星辰。</t>
         </is>
       </c>
       <c r="H233" s="3" t="n">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>龙须鲤是灵鱼一脉的9级材料。</t>
+          <t>龙须鲤鱼须修长如龙须，鳞片间流动着淡淡金光。</t>
         </is>
       </c>
       <c r="H234" s="3" t="n">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>凤尾锦鲤是灵鱼一脉的10级材料。</t>
+          <t>凤尾锦鲤尾鳍舒展如羽，游动时映出绚丽霞色。</t>
         </is>
       </c>
       <c r="H235" s="3" t="n">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>九幽玄鱼是灵鱼一脉的11级材料。</t>
+          <t>九幽玄鱼鱼身幽黑，九道暗纹随水波明灭。</t>
         </is>
       </c>
       <c r="H236" s="3" t="n">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>扶桑金鲤是灵鱼一脉的12级材料。</t>
+          <t>扶桑金鲤鳞片灿金，游过水面会留下暖红光痕。</t>
         </is>
       </c>
       <c r="H237" s="3" t="n">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>建木游龙是灵鱼一脉的13级材料。</t>
+          <t>建木游龙鱼身修长似龙，鳞脊生有青色木纹。</t>
         </is>
       </c>
       <c r="H238" s="3" t="n">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>菩提慧鱼是灵鱼一脉的14级材料。</t>
+          <t>菩提慧鱼额心一点灵光，游近时令人神思澄明。</t>
         </is>
       </c>
       <c r="H239" s="3" t="n">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙鲲苗是灵鱼一脉的15级材料。</t>
+          <t>鸿蒙鲲苗虽是幼鲲，背鳍已能卷起清浊水潮。</t>
         </is>
       </c>
       <c r="H240" s="3" t="n">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>太初神鲲是灵鱼一脉的16级材料。</t>
+          <t>太初神鲲体内仿佛藏着无边水域，鳞光随气机变化。</t>
         </is>
       </c>
       <c r="H241" s="3" t="n">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>清水灵珠是灵珠一脉的1级材料。</t>
+          <t>清水灵珠珠体清透如泉，轻晃时内有水纹荡漾。</t>
         </is>
       </c>
       <c r="H242" s="3" t="n">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>青波珠是灵珠一脉的2级材料。</t>
+          <t>青波珠珠面泛着青色波光，触手清凉。</t>
         </is>
       </c>
       <c r="H243" s="3" t="n">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>赤潮珠是灵珠一脉的3级材料。</t>
+          <t>赤潮珠珠心赤红，光泽如潮汐起伏。</t>
         </is>
       </c>
       <c r="H244" s="3" t="n">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>月华珠是灵珠一脉的4级材料。</t>
+          <t>月华珠月华凝于珠中，夜色下清辉不散。</t>
         </is>
       </c>
       <c r="H245" s="3" t="n">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>雷鸣珠是灵珠一脉的5级材料。</t>
+          <t>雷鸣珠珠内封着细小雷弧，靠近便有低鸣。</t>
         </is>
       </c>
       <c r="H246" s="3" t="n">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>玄冰珠是灵珠一脉的6级材料。</t>
+          <t>玄冰珠由冰魄凝成，寒气沿珠面缓缓流动。</t>
         </is>
       </c>
       <c r="H247" s="3" t="n">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>地泉珠是灵珠一脉的7级材料。</t>
+          <t>地泉珠中仿佛藏着一眼地泉，土金色光泽沉静厚重。</t>
         </is>
       </c>
       <c r="H248" s="3" t="n">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>星澜珠是灵珠一脉的8级材料。</t>
+          <t>星澜珠聚起星辉澜纹，转动时满珠星点闪烁。</t>
         </is>
       </c>
       <c r="H249" s="3" t="n">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>龙涎珠是灵珠一脉的9级材料。</t>
+          <t>龙涎珠珠心凝着龙涎，淡金光芒如游龙盘旋。</t>
         </is>
       </c>
       <c r="H250" s="3" t="n">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>凤泪珠是灵珠一脉的10级材料。</t>
+          <t>凤泪珠晶莹温润，光下泛起凤羽般的赤金。</t>
         </is>
       </c>
       <c r="H251" s="3" t="n">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>九幽玄珠是灵珠一脉的11级材料。</t>
+          <t>九幽玄珠珠色深幽，内里九重暗环层层相套。</t>
         </is>
       </c>
       <c r="H252" s="3" t="n">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>扶桑日珠是灵珠一脉的12级材料。</t>
+          <t>扶桑日珠珠光炽烈如朝阳，表面流动着金红日纹。</t>
         </is>
       </c>
       <c r="H253" s="3" t="n">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>建木碧珠是灵珠一脉的13级材料。</t>
+          <t>建木碧珠珠中生有木脉纹，灵气沿纹路循环。</t>
         </is>
       </c>
       <c r="H254" s="3" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>菩提心珠是灵珠一脉的14级材料。</t>
+          <t>菩提心珠珠心澄净，静观片刻便觉杂念渐消。</t>
         </is>
       </c>
       <c r="H255" s="3" t="n">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙源珠是灵珠一脉的15级材料。</t>
+          <t>鸿蒙源珠珠内清浊二气相依旋转，始终不相混。</t>
         </is>
       </c>
       <c r="H256" s="3" t="n">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>太初神珠是灵珠一脉的16级材料。</t>
+          <t>太初神珠五色微光交汇，仿佛映出天地初始的轮廓。</t>
         </is>
       </c>
       <c r="H257" s="3" t="n">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>青白玉是玉石一脉的1级材料。</t>
+          <t>青白玉玉质青白温润，握在手中有淡淡凉意。</t>
         </is>
       </c>
       <c r="H258" s="3" t="n">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>云纹玉是玉石一脉的2级材料。</t>
+          <t>云纹玉玉面云纹舒卷，随光线变幻深浅。</t>
         </is>
       </c>
       <c r="H259" s="3" t="n">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>赤霞玉是玉石一脉的3级材料。</t>
+          <t>赤霞玉玉中藏着赤霞，转动时如晚云流动。</t>
         </is>
       </c>
       <c r="H260" s="3" t="n">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>月华玉是玉石一脉的4级材料。</t>
+          <t>月华玉玉色皎洁，夜间会映出柔和月光。</t>
         </is>
       </c>
       <c r="H261" s="3" t="n">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>雷纹玉是玉石一脉的5级材料。</t>
+          <t>雷纹玉表面交织雷纹，指尖触碰便有麻意。</t>
         </is>
       </c>
       <c r="H262" s="3" t="n">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>玄冰玉是玉石一脉的6级材料。</t>
+          <t>玄冰玉玉质清寒如冰，内里封着细碎霜花。</t>
         </is>
       </c>
       <c r="H263" s="3" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>地髓玉是玉石一脉的7级材料。</t>
+          <t>地髓玉玉髓厚重，纹理仿佛山根与地脉交错。</t>
         </is>
       </c>
       <c r="H264" s="3" t="n">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>星辉玉是玉石一脉的8级材料。</t>
+          <t>星辉玉玉心点点星辉，暗处仍能映出微光。</t>
         </is>
       </c>
       <c r="H265" s="3" t="n">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>龙血玉是玉石一脉的9级材料。</t>
+          <t>龙血玉玉色深红，内部凝着蜿蜒龙血纹。</t>
         </is>
       </c>
       <c r="H266" s="3" t="n">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>凤栖玉是玉石一脉的10级材料。</t>
+          <t>凤栖玉玉面金红相间，纹理舒展如凤羽。</t>
         </is>
       </c>
       <c r="H267" s="3" t="n">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>九幽玄玉是玉石一脉的11级材料。</t>
+          <t>九幽玄玉玉质幽黑，九道玄纹从中心向外延伸。</t>
         </is>
       </c>
       <c r="H268" s="3" t="n">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>扶桑阳玉是玉石一脉的12级材料。</t>
+          <t>扶桑阳玉玉中蕴着暖阳，握久后掌心微温。</t>
         </is>
       </c>
       <c r="H269" s="3" t="n">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>建木碧玉是玉石一脉的13级材料。</t>
+          <t>建木碧玉透出青色木纹，灵气如枝脉分叉。</t>
         </is>
       </c>
       <c r="H270" s="3" t="n">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>菩提心玉是玉石一脉的14级材料。</t>
+          <t>菩提心玉玉心清宁，靠近时仿佛能听见木叶轻响。</t>
         </is>
       </c>
       <c r="H271" s="3" t="n">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙源玉是玉石一脉的15级材料。</t>
+          <t>鸿蒙源玉玉内清浊云气交叠，颜色随光线缓缓变幻。</t>
         </is>
       </c>
       <c r="H272" s="3" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>太初神玉是玉石一脉的16级材料。</t>
+          <t>太初神玉温润无瑕，内部隐约浮现初生天地的微光。</t>
         </is>
       </c>
       <c r="H273" s="3" t="n">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>浅砂矿口以河砂与碎岩筑成，矿壁留有新凿出的浅痕，并有四分之一概率产出玉石。</t>
+          <t>浅砂矿口以河砂与碎岩筑成，矿壁留有新凿出的浅痕。</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr"/>
@@ -23759,7 +23759,7 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>乌铁矿井立于溪谷缓坡，井下回声沉闷如钟，并有四分之一概率产出玉石。</t>
+          <t>乌铁矿井立于溪谷缓坡，井下回声沉闷如钟。</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>匠人取月银石柱建成月银矿洞，洞顶在月夜泛出银辉，并有四分之一概率产出玉石。</t>
+          <t>匠人取月银石柱建成月银矿洞，洞顶在月夜泛出银辉。</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr"/>
@@ -23847,7 +23847,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>传闻白金矿脉旧址在云崖石台，金脉沿岩层纵横生长，并有四分之一概率产出玉石。</t>
+          <t>传闻白金矿脉旧址在云崖石台，金脉沿岩层纵横生长。</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr"/>
@@ -23891,7 +23891,7 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>寒谷背阴处所见的冰陨深井由冰陨石与寒木构成，井口吐出的风带着冰屑，并有四分之一概率产出玉石。</t>
+          <t>寒谷背阴处所见的冰陨深井由冰陨石与寒木构成，井口吐出的风带着冰屑。</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr"/>
@@ -23935,7 +23935,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>地火晶窟以地火岩与赤铜筑成，晶窟深处常有红光跃动，并有四分之一概率产出玉石。</t>
+          <t>地火晶窟以地火岩与赤铜筑成，晶窟深处常有红光跃动。</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr"/>
@@ -23979,7 +23979,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>青罡玉坑立于苍梧秘境，玉壁内云纹缓缓迁移，并有四分之一概率产出玉石。</t>
+          <t>青罡玉坑立于苍梧秘境，玉壁内云纹缓缓迁移。</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr"/>
@@ -24023,7 +24023,7 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>匠人取雷极砂砖建成雷极砂场，砂层摩擦时传来细雷，并有四分之一概率产出玉石。</t>
+          <t>匠人取雷极砂砖建成雷极砂场，砂层摩擦时传来细雷。</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr"/>
@@ -24067,7 +24067,7 @@
       </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>传闻坤髓矿府旧址在坤元地脉，地脉气息沿矿壁缓缓升起，并有四分之一概率产出玉石。</t>
+          <t>传闻坤髓矿府旧址在坤元地脉，地脉气息沿矿壁缓缓升起。</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr"/>
@@ -24111,7 +24111,7 @@
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>星落天原所见的星陨矿坑由星陨铁与天河砂构成，夜间矿壁会映出群星轨迹，并有四分之一概率产出玉石。</t>
+          <t>星落天原所见的星陨矿坑由星陨铁与天河砂构成，夜间矿壁会映出群星轨迹。</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>太虚玉窟以紫府玉与烟霞木筑成，紫色云烟常在矿壁周围盘旋，并有四分之一概率产出玉石。</t>
+          <t>太虚玉窟以紫府玉与烟霞木筑成，紫色云烟常在矿壁周围盘旋。</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr"/>
@@ -24199,7 +24199,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>九幽铁渊立于九曲地宫，矿壁依九曲方位层层展开，并有四分之一概率产出玉石。</t>
+          <t>九幽铁渊立于九曲地宫，矿壁依九曲方位层层展开。</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr"/>
@@ -24243,7 +24243,7 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>匠人取涅火晶与赤金建成日精金脉，赤金纹路随天火明灭不定，并有四分之一概率产出玉石。</t>
+          <t>匠人取涅火晶与赤金建成日精金脉，赤金纹路随天火明灭不定。</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr"/>
@@ -24287,7 +24287,7 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>传闻月魄玉山旧址在龙眠古渊，矿壁上隐约盘着龙形云气，并有四分之一概率产出玉石。</t>
+          <t>传闻月魄玉山旧址在龙眠古渊，矿壁上隐约盘着龙形云气。</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr"/>
@@ -24331,7 +24331,7 @@
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>凤栖神木所见的天河砂海由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过，并有四分之一概率产出玉石。</t>
+          <t>凤栖神木所见的天河砂海由凤羽晶与梧桐神木构成，高处常有凤鸟虚影掠过。</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr"/>
@@ -24375,7 +24375,7 @@
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙晶域以太初晶与鸿蒙母金筑成，近看矿壁仿佛隔着太初雾海，并有四分之一概率产出玉石。</t>
+          <t>鸿蒙晶域以太初晶与鸿蒙母金筑成，近看矿壁仿佛隔着太初雾海。</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr"/>
